--- a/artfynd/A 67432-2021 artfynd.xlsx
+++ b/artfynd/A 67432-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 67432-2021 artfynd.xlsx
+++ b/artfynd/A 67432-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1492,14 +1492,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>25196</v>
+        <v>82402785</v>
       </c>
       <c r="B9" t="n">
         <v>57576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1528,17 +1528,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Störlinge Gran, mindre kärr, Öl</t>
+          <t>58, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607647.5722426042</v>
+        <v>607648.1065484625</v>
       </c>
       <c r="R9" t="n">
-        <v>6297450.627733494</v>
+        <v>6297451.189158756</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2014-04-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
+          <t>2014-04-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1580,8 +1580,13 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uttorkat, inget vatten</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
@@ -1592,12 +1597,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helena Lager</t>
+          <t>Pia Hertonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ingemar Ahlén</t>
+          <t>Pia Hertonsson, Marika Stenberg, Erik Fridolf, Per Nyström, Lars-Göran Pärlklint</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1840,53 +1845,56 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>82402785</v>
+        <v>90375525</v>
       </c>
       <c r="B12" t="n">
-        <v>57576</v>
+        <v>90319</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100117</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana dalmatina</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bonaparte, 1840</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>58, Öl</t>
+          <t>Störlinge, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607648.1065484625</v>
+        <v>607594.5574460324</v>
       </c>
       <c r="R12" t="n">
-        <v>6297451.189158756</v>
+        <v>6297229.096724058</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,7 +1918,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2014-04-15</t>
+          <t>2017-10-09</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1920,7 +1928,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2014-04-15</t>
+          <t>2017-10-09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -1928,39 +1936,35 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Uttorkat, inget vatten</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Pia Hertonsson</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pia Hertonsson, Marika Stenberg, Erik Fridolf, Per Nyström, Lars-Göran Pärlklint</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>90375525</v>
+        <v>90375503</v>
       </c>
       <c r="B13" t="n">
-        <v>90319</v>
+        <v>98520</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,26 +1977,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2073,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>90375503</v>
+        <v>90375515</v>
       </c>
       <c r="B14" t="n">
-        <v>98520</v>
+        <v>107997</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,21 +2094,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2190,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>90375515</v>
+        <v>112272267</v>
       </c>
       <c r="B15" t="n">
-        <v>107997</v>
+        <v>99036</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,21 +2211,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2230,17 +2235,17 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Störlinge, Öl</t>
+          <t>Störlinge gran, Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607594.5574460324</v>
+        <v>607474</v>
       </c>
       <c r="R15" t="n">
-        <v>6297229.096724058</v>
+        <v>6297135</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2264,22 +2269,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2295,22 +2290,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112272267</v>
+        <v>112272399</v>
       </c>
       <c r="B16" t="n">
-        <v>99036</v>
+        <v>108631</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,21 +2318,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2351,10 +2346,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607474</v>
+        <v>607628</v>
       </c>
       <c r="R16" t="n">
-        <v>6297135</v>
+        <v>6297526</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2414,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112272399</v>
+        <v>112272269</v>
       </c>
       <c r="B17" t="n">
-        <v>108631</v>
+        <v>96761</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,21 +2425,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2458,10 +2453,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607628</v>
+        <v>607474</v>
       </c>
       <c r="R17" t="n">
-        <v>6297526</v>
+        <v>6297135</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2518,113 +2513,6 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>112272269</v>
-      </c>
-      <c r="B18" t="n">
-        <v>96761</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>219798</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Epipactis helleborine</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Störlinge gran, Öl</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>607474</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6297135</v>
-      </c>
-      <c r="S18" t="n">
-        <v>25</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Borgholm</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Gärdslösa</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 67432-2021 artfynd.xlsx
+++ b/artfynd/A 67432-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2219488</v>
+        <v>375393</v>
       </c>
       <c r="B2" t="n">
-        <v>108193</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>1307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grov gulmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Drepanocladus lycopodioides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Störlinge gran, Öl</t>
+          <t>KÄRR 700 M NV TJUSHÖG 2 KM NO GÄRDSLÖSA KA, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607664.4073008539</v>
+        <v>607604</v>
       </c>
       <c r="R2" t="n">
-        <v>6297201.86788195</v>
+        <v>6297331</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-05-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-05-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>H04H9B02:1:1/riklig(1)/dominerande(1)/-1</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,33 +764,32 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Tidvis översvämmad mark/Tidvis översvämmad mark av vät-typ</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
+          <t>Våtmarksinventeringen (vmi)</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Våtmarksinventeringen H-län (grundinventeringen)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2154616</v>
+        <v>57702099</v>
       </c>
       <c r="B3" t="n">
-        <v>107996</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +797,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>2676</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Störlinge gran, Öl</t>
+          <t>Störlinge Gran, NV delen, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607664.4073008539</v>
+        <v>607665</v>
       </c>
       <c r="R3" t="n">
-        <v>6297201.86788195</v>
+        <v>6297550</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-05-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-05-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,36 +870,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
+          <t>Per Backman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
+          <t>Per Backman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2643646</v>
+        <v>57716521</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +897,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>2779</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Störlinge gran, Öl</t>
+          <t>Störlinge Gran, NV delen, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607714.9707725289</v>
+        <v>607665</v>
       </c>
       <c r="R4" t="n">
-        <v>6297092.535004315</v>
+        <v>6297550</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2009-05-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2009-05-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,36 +970,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
+          <t>Per Backman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
+          <t>Per Backman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2643647</v>
+        <v>67859293</v>
       </c>
       <c r="B5" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,37 +997,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Störlinge gran, Öl</t>
+          <t>Störlinge Gran, 300m N sjögatan, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607626.7239965091</v>
+        <v>607439</v>
       </c>
       <c r="R5" t="n">
-        <v>6297130.79184048</v>
+        <v>6297185</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,22 +1057,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2009-05-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2009-05-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,38 +1071,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
+          <t>Per Backman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
+          <t>Per Backman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>57683342</v>
+        <v>90375525</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,44 +1101,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Störlinge Gran, NV delen, Öl</t>
+          <t>Störlinge, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607665.3250664109</v>
+        <v>607595</v>
       </c>
       <c r="R6" t="n">
-        <v>6297549.66306082</v>
+        <v>6297229</v>
       </c>
       <c r="S6" t="n">
-        <v>181</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,22 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-03-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-03-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,33 +1172,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>57702099</v>
+        <v>25195</v>
       </c>
       <c r="B7" t="n">
-        <v>92895</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,40 +1202,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2676</v>
+        <v>100117</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Rana dalmatina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>Bonaparte, 1840</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Störlinge Gran, NV delen, Öl</t>
+          <t>Stora kärret i Störlinge Gran, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607665.3250664109</v>
+        <v>607569</v>
       </c>
       <c r="R7" t="n">
-        <v>6297549.66306082</v>
+        <v>6297370</v>
       </c>
       <c r="S7" t="n">
-        <v>181</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,22 +1256,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-03-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-03-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,27 +1276,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Helena Lager</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Ingemar Ahlén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>57716521</v>
+        <v>25196</v>
       </c>
       <c r="B8" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,40 +1299,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2779</v>
+        <v>100117</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Rana dalmatina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Bonaparte, 1840</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Störlinge Gran, NV delen, Öl</t>
+          <t>Störlinge Gran, mindre kärr, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607665.3250664109</v>
+        <v>607648</v>
       </c>
       <c r="R8" t="n">
-        <v>6297549.66306082</v>
+        <v>6297451</v>
       </c>
       <c r="S8" t="n">
-        <v>181</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,22 +1353,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2016-03-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2016-03-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,65 +1373,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Helena Lager</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Ingemar Ahlén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>82402785</v>
+        <v>2154616</v>
       </c>
       <c r="B9" t="n">
-        <v>57576</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100117</v>
+        <v>219677</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana dalmatina</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bonaparte, 1840</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>58, Öl</t>
+          <t>Störlinge gran, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607648.1065484625</v>
+        <v>607664</v>
       </c>
       <c r="R9" t="n">
-        <v>6297451.189158756</v>
+        <v>6297202</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,100 +1450,93 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-04-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-05-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-04-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Uttorkat, inget vatten</t>
+          <t>2009-05-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pia Hertonsson</t>
+          <t>Åke Rühling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Hertonsson, Marika Stenberg, Erik Fridolf, Per Nyström, Lars-Göran Pärlklint</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>82402784</v>
+        <v>90375515</v>
       </c>
       <c r="B10" t="n">
-        <v>57576</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100117</v>
+        <v>219677</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana dalmatina</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bonaparte, 1840</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>59, Öl</t>
+          <t>Störlinge, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607568.9854549651</v>
+        <v>607595</v>
       </c>
       <c r="R10" t="n">
-        <v>6297369.740130902</v>
+        <v>6297229</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1679,62 +1560,47 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-04-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-04-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Uttorkat, inget vatten</t>
+          <t>2017-10-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pia Hertonsson</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Hertonsson, Marika Stenberg, Erik Fridolf, Per Nyström, Lars-Göran Pärlklint</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>67859293</v>
+        <v>112272399</v>
       </c>
       <c r="B11" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,43 +1608,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4405</v>
+        <v>219677</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Störlinge Gran, 300m N sjögatan, Öl</t>
+          <t>Störlinge gran, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607439.2951919489</v>
+        <v>607628</v>
       </c>
       <c r="R11" t="n">
-        <v>6297184.573187537</v>
+        <v>6297526</v>
       </c>
       <c r="S11" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,22 +1666,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-10-03</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-10-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,68 +1687,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>90375525</v>
+        <v>2219488</v>
       </c>
       <c r="B12" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>219711</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Störlinge, Öl</t>
+          <t>Störlinge gran, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607594.5574460324</v>
+        <v>607664</v>
       </c>
       <c r="R12" t="n">
-        <v>6297229.096724058</v>
+        <v>6297202</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1918,22 +1764,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-05-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-05-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,34 +1778,37 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Åke Rühling</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>90375503</v>
+        <v>112272269</v>
       </c>
       <c r="B13" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,21 +1816,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2001,17 +1840,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Störlinge, Öl</t>
+          <t>Störlinge gran, Öl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607594.5574460324</v>
+        <v>607474</v>
       </c>
       <c r="R13" t="n">
-        <v>6297229.096724058</v>
+        <v>6297135</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2035,22 +1874,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,27 +1895,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>90375515</v>
+        <v>2643646</v>
       </c>
       <c r="B14" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,41 +1918,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219677</v>
+        <v>219862</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Störlinge, Öl</t>
+          <t>Störlinge gran, Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607594.5574460324</v>
+        <v>607715</v>
       </c>
       <c r="R14" t="n">
-        <v>6297229.096724058</v>
+        <v>6297093</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2152,22 +1972,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-05-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-05-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,34 +1986,37 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Åke Rühling</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112272267</v>
+        <v>2643647</v>
       </c>
       <c r="B15" t="n">
-        <v>99036</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,38 +2024,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Störlinge gran, Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607474</v>
+        <v>607627</v>
       </c>
       <c r="R15" t="n">
-        <v>6297135</v>
+        <v>6297131</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2269,12 +2078,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2009-05-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2009-05-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,34 +2092,37 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Åke Rühling</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112272399</v>
+        <v>57683342</v>
       </c>
       <c r="B16" t="n">
-        <v>108631</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,41 +2130,44 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Störlinge gran, Öl</t>
+          <t>Störlinge Gran, NV delen, Öl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607628</v>
+        <v>607665</v>
       </c>
       <c r="R16" t="n">
-        <v>6297526</v>
+        <v>6297550</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2376,12 +2191,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2016-03-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2016-03-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,34 +2205,32 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Per Backman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112272269</v>
+        <v>90375503</v>
       </c>
       <c r="B17" t="n">
-        <v>96761</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,21 +2238,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2449,17 +2262,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Störlinge gran, Öl</t>
+          <t>Störlinge, Öl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607474</v>
+        <v>607595</v>
       </c>
       <c r="R17" t="n">
-        <v>6297135</v>
+        <v>6297229</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2483,12 +2296,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2017-10-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2017-10-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,15 +2317,121 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>112272267</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Störlinge gran, Öl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>607474</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6297135</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 67432-2021 artfynd.xlsx
+++ b/artfynd/A 67432-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Våtmarksinventeringen H-län (grundinventeringen)</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/375393</t>
         </is>
       </c>
     </row>
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57702099</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57716521</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67859293</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90375525</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/25195</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/25196</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2154616</t>
         </is>
       </c>
     </row>
@@ -1594,6 +1639,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90375515</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112272399</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1800,6 +1855,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2219488</t>
         </is>
       </c>
     </row>
@@ -1904,6 +1964,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112272269</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2010,6 +2075,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2643646</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2643647</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2222,6 +2297,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57683342</t>
         </is>
       </c>
     </row>
@@ -2330,6 +2410,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90375503</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2432,8 +2517,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112272267</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>